--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="16220" activeTab="1"/>
+    <workbookView windowWidth="28000" windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -717,7 +717,7 @@
     <t>5、点击屏幕底部待办，切换到待办页</t>
   </si>
   <si>
-    <t>6、点击新建按钮，拉起小艺输入法</t>
+    <t>6、点击新建按钮，拉起输入法</t>
   </si>
   <si>
     <t>7、26键盘输入test，点击键盘上的回车按钮</t>
@@ -11008,7 +11008,7 @@
       <c r="A373" s="11"/>
       <c r="B373" s="11"/>
       <c r="C373" s="11"/>
-      <c r="D373" s="11" t="s">
+      <c r="D373" s="12" t="s">
         <v>402</v>
       </c>
     </row>
@@ -11016,7 +11016,7 @@
       <c r="A374" s="11"/>
       <c r="B374" s="11"/>
       <c r="C374" s="11"/>
-      <c r="D374" s="11" t="s">
+      <c r="D374" s="12" t="s">
         <v>403</v>
       </c>
     </row>
@@ -26415,7 +26415,7 @@
       <c r="C29" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="D29" s="7"/>
+      <c r="D29" s="5"/>
     </row>
     <row r="30" ht="17" spans="1:4">
       <c r="A30" s="3" t="s">
@@ -26427,7 +26427,7 @@
       <c r="C30" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="D30" s="7"/>
+      <c r="D30" s="5"/>
     </row>
     <row r="31" ht="17" spans="1:4">
       <c r="A31" s="3" t="s">
@@ -26439,7 +26439,7 @@
       <c r="C31" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D31" s="7"/>
+      <c r="D31" s="5"/>
     </row>
     <row r="32" ht="17" spans="1:4">
       <c r="A32" s="3" t="s">
@@ -26451,7 +26451,7 @@
       <c r="C32" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="D32" s="7"/>
+      <c r="D32" s="5"/>
     </row>
     <row r="33" ht="17" spans="1:4">
       <c r="A33" s="3" t="s">
@@ -26463,7 +26463,7 @@
       <c r="C33" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="D33" s="7"/>
+      <c r="D33" s="5"/>
     </row>
     <row r="34" ht="17" spans="1:4">
       <c r="A34" s="3" t="s">
@@ -26475,7 +26475,7 @@
       <c r="C34" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="D34" s="7"/>
+      <c r="D34" s="5"/>
     </row>
     <row r="35" ht="17" spans="1:4">
       <c r="A35" s="3" t="s">
@@ -26487,7 +26487,7 @@
       <c r="C35" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="D35" s="7"/>
+      <c r="D35" s="5"/>
     </row>
     <row r="36" ht="17" spans="1:4">
       <c r="A36" s="3" t="s">
@@ -26499,7 +26499,7 @@
       <c r="C36" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="D36" s="7"/>
+      <c r="D36" s="5"/>
     </row>
     <row r="37" ht="17" spans="1:4">
       <c r="A37" s="3" t="s">
@@ -26511,7 +26511,7 @@
       <c r="C37" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D37" s="7"/>
+      <c r="D37" s="5"/>
     </row>
     <row r="38" ht="17" spans="1:4">
       <c r="A38" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28000" windowHeight="16220"/>
+    <workbookView windowWidth="32000" windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -1179,7 +1179,7 @@
     <t>相机咨询小艺实现拍照</t>
   </si>
   <si>
-    <t>2、点击尝试AI唤起siri</t>
+    <t>2、点击尝试AI唤起小爱同学</t>
   </si>
   <si>
     <t>3、点击输入并发送我要拍夕阳应该怎么拍</t>
@@ -1291,7 +1291,7 @@
     <t>2、主页浏览，上下各滑动1次，循环5次</t>
   </si>
   <si>
-    <t>3、点击收付款</t>
+    <t>3、点击收付款，并返回</t>
   </si>
   <si>
     <t>4、点击扫一扫</t>
@@ -26523,7 +26523,7 @@
       <c r="C38" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="D38" s="7"/>
+      <c r="D38" s="5"/>
     </row>
     <row r="39" ht="17" spans="1:4">
       <c r="A39" s="3" t="s">
@@ -26535,7 +26535,7 @@
       <c r="C39" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="D39" s="7"/>
+      <c r="D39" s="5"/>
     </row>
     <row r="40" ht="17" spans="1:4">
       <c r="A40" s="3" t="s">
@@ -26547,7 +26547,7 @@
       <c r="C40" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="D40" s="7"/>
+      <c r="D40" s="5"/>
     </row>
     <row r="41" ht="17" spans="1:4">
       <c r="A41" s="3" t="s">
@@ -26559,7 +26559,7 @@
       <c r="C41" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="D41" s="7"/>
+      <c r="D41" s="5"/>
     </row>
     <row r="42" ht="17" spans="1:4">
       <c r="A42" s="3" t="s">
@@ -26571,7 +26571,7 @@
       <c r="C42" s="3" t="s">
         <v>289</v>
       </c>
-      <c r="D42" s="7"/>
+      <c r="D42" s="5"/>
     </row>
     <row r="43" ht="17" spans="1:4">
       <c r="A43" s="3" t="s">
@@ -26583,7 +26583,7 @@
       <c r="C43" s="3" t="s">
         <v>299</v>
       </c>
-      <c r="D43" s="7"/>
+      <c r="D43" s="5"/>
     </row>
     <row r="44" ht="17" spans="1:4">
       <c r="A44" s="3" t="s">
@@ -26595,7 +26595,7 @@
       <c r="C44" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="D44" s="7"/>
+      <c r="D44" s="5"/>
     </row>
     <row r="45" ht="17" spans="1:4">
       <c r="A45" s="3" t="s">
@@ -26607,7 +26607,7 @@
       <c r="C45" s="3" t="s">
         <v>332</v>
       </c>
-      <c r="D45" s="7"/>
+      <c r="D45" s="5"/>
     </row>
     <row r="46" ht="17" spans="1:4">
       <c r="A46" s="3" t="s">
@@ -26619,7 +26619,7 @@
       <c r="C46" s="3" t="s">
         <v>339</v>
       </c>
-      <c r="D46" s="7"/>
+      <c r="D46" s="5"/>
     </row>
     <row r="47" ht="17" spans="1:4">
       <c r="A47" s="3" t="s">
@@ -26631,7 +26631,7 @@
       <c r="C47" s="3" t="s">
         <v>363</v>
       </c>
-      <c r="D47" s="7"/>
+      <c r="D47" s="5"/>
     </row>
     <row r="48" ht="17" spans="1:4">
       <c r="A48" s="3" t="s">
@@ -26643,7 +26643,7 @@
       <c r="C48" s="3" t="s">
         <v>382</v>
       </c>
-      <c r="D48" s="7"/>
+      <c r="D48" s="5"/>
     </row>
     <row r="49" ht="17" spans="1:4">
       <c r="A49" s="3" t="s">
@@ -26655,7 +26655,7 @@
       <c r="C49" s="3" t="s">
         <v>398</v>
       </c>
-      <c r="D49" s="7"/>
+      <c r="D49" s="5"/>
     </row>
     <row r="50" ht="17" spans="1:4">
       <c r="A50" s="3" t="s">
@@ -26667,7 +26667,7 @@
       <c r="C50" s="3" t="s">
         <v>422</v>
       </c>
-      <c r="D50" s="7"/>
+      <c r="D50" s="5"/>
     </row>
     <row r="51" ht="17" spans="1:4">
       <c r="A51" s="3" t="s">
@@ -26679,7 +26679,7 @@
       <c r="C51" s="3" t="s">
         <v>437</v>
       </c>
-      <c r="D51" s="7"/>
+      <c r="D51" s="5"/>
     </row>
     <row r="52" ht="17" spans="1:4">
       <c r="A52" s="3" t="s">
@@ -26691,7 +26691,7 @@
       <c r="C52" s="3" t="s">
         <v>412</v>
       </c>
-      <c r="D52" s="7"/>
+      <c r="D52" s="5"/>
     </row>
     <row r="53" ht="17" spans="1:4">
       <c r="A53" s="3" t="s">
@@ -26703,7 +26703,7 @@
       <c r="C53" s="3" t="s">
         <v>448</v>
       </c>
-      <c r="D53" s="7"/>
+      <c r="D53" s="5"/>
     </row>
     <row r="54" ht="17" spans="1:4">
       <c r="A54" s="3" t="s">
@@ -26715,7 +26715,7 @@
       <c r="C54" s="3" t="s">
         <v>695</v>
       </c>
-      <c r="D54" s="7"/>
+      <c r="D54" s="5"/>
     </row>
     <row r="55" ht="17" spans="1:4">
       <c r="A55" s="3" t="s">
@@ -26727,7 +26727,7 @@
       <c r="C55" s="3" t="s">
         <v>704</v>
       </c>
-      <c r="D55" s="7"/>
+      <c r="D55" s="5"/>
     </row>
     <row r="56" ht="17" spans="1:4">
       <c r="A56" s="3" t="s">
@@ -26739,7 +26739,7 @@
       <c r="C56" s="3" t="s">
         <v>1190</v>
       </c>
-      <c r="D56" s="7"/>
+      <c r="D56" s="5"/>
     </row>
     <row r="57" ht="17" spans="1:4">
       <c r="A57" s="3" t="s">
@@ -26751,7 +26751,7 @@
       <c r="C57" s="3" t="s">
         <v>1210</v>
       </c>
-      <c r="D57" s="7"/>
+      <c r="D57" s="5"/>
     </row>
     <row r="58" ht="17" spans="1:4">
       <c r="A58" s="3" t="s">
@@ -27605,7 +27605,7 @@
       </c>
       <c r="D128" s="8"/>
     </row>
-    <row r="129" ht="17" spans="1:5">
+    <row r="129" ht="17" spans="1:4">
       <c r="A129" s="3" t="s">
         <v>1669</v>
       </c>
@@ -27617,7 +27617,7 @@
       </c>
       <c r="D129" s="8"/>
     </row>
-    <row r="130" ht="17" spans="1:5">
+    <row r="130" ht="17" spans="1:4">
       <c r="A130" s="3" t="s">
         <v>1669</v>
       </c>
@@ -27629,7 +27629,7 @@
       </c>
       <c r="D130" s="8"/>
     </row>
-    <row r="131" ht="17" spans="1:5">
+    <row r="131" ht="17" spans="1:4">
       <c r="A131" s="3" t="s">
         <v>1722</v>
       </c>
@@ -27641,7 +27641,7 @@
       </c>
       <c r="D131" s="8"/>
     </row>
-    <row r="132" ht="17" spans="1:5">
+    <row r="132" ht="17" spans="1:4">
       <c r="A132" s="3" t="s">
         <v>1722</v>
       </c>
@@ -27653,7 +27653,7 @@
       </c>
       <c r="D132" s="8"/>
     </row>
-    <row r="133" ht="17" spans="1:5">
+    <row r="133" ht="17" spans="1:4">
       <c r="A133" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27664,9 +27664,8 @@
         <v>1747</v>
       </c>
       <c r="D133" s="8"/>
-      <c r="E133" s="9"/>
-    </row>
-    <row r="134" ht="17" spans="1:5">
+    </row>
+    <row r="134" ht="17" spans="1:4">
       <c r="A134" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27677,9 +27676,8 @@
         <v>1763</v>
       </c>
       <c r="D134" s="8"/>
-      <c r="E134" s="9"/>
-    </row>
-    <row r="135" ht="17" spans="1:5">
+    </row>
+    <row r="135" ht="17" spans="1:4">
       <c r="A135" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27690,9 +27688,8 @@
         <v>1777</v>
       </c>
       <c r="D135" s="8"/>
-      <c r="E135" s="9"/>
-    </row>
-    <row r="136" ht="17" spans="1:5">
+    </row>
+    <row r="136" ht="17" spans="1:4">
       <c r="A136" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27703,9 +27700,8 @@
         <v>1793</v>
       </c>
       <c r="D136" s="8"/>
-      <c r="E136" s="9"/>
-    </row>
-    <row r="137" ht="17" spans="1:5">
+    </row>
+    <row r="137" ht="17" spans="1:4">
       <c r="A137" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27716,9 +27712,8 @@
         <v>1810</v>
       </c>
       <c r="D137" s="8"/>
-      <c r="E137" s="9"/>
-    </row>
-    <row r="138" ht="17" spans="1:5">
+    </row>
+    <row r="138" ht="17" spans="1:4">
       <c r="A138" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27729,9 +27724,8 @@
         <v>1822</v>
       </c>
       <c r="D138" s="8"/>
-      <c r="E138" s="9"/>
-    </row>
-    <row r="139" ht="17" spans="1:5">
+    </row>
+    <row r="139" ht="17" spans="1:4">
       <c r="A139" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27742,9 +27736,8 @@
         <v>1837</v>
       </c>
       <c r="D139" s="8"/>
-      <c r="E139" s="9"/>
-    </row>
-    <row r="140" ht="17" spans="1:5">
+    </row>
+    <row r="140" ht="17" spans="1:4">
       <c r="A140" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27755,9 +27748,8 @@
         <v>1845</v>
       </c>
       <c r="D140" s="8"/>
-      <c r="E140" s="9"/>
-    </row>
-    <row r="141" ht="17" spans="1:5">
+    </row>
+    <row r="141" ht="17" spans="1:4">
       <c r="A141" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27768,9 +27760,8 @@
         <v>1857</v>
       </c>
       <c r="D141" s="8"/>
-      <c r="E141" s="9"/>
-    </row>
-    <row r="142" ht="17" spans="1:5">
+    </row>
+    <row r="142" ht="17" spans="1:4">
       <c r="A142" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27781,9 +27772,8 @@
         <v>1866</v>
       </c>
       <c r="D142" s="8"/>
-      <c r="E142" s="9"/>
-    </row>
-    <row r="143" ht="17" spans="1:5">
+    </row>
+    <row r="143" ht="17" spans="1:4">
       <c r="A143" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27794,9 +27784,8 @@
         <v>1879</v>
       </c>
       <c r="D143" s="8"/>
-      <c r="E143" s="9"/>
-    </row>
-    <row r="144" ht="17" spans="1:5">
+    </row>
+    <row r="144" ht="17" spans="1:4">
       <c r="A144" s="3" t="s">
         <v>1745</v>
       </c>
@@ -27807,7 +27796,6 @@
         <v>1892</v>
       </c>
       <c r="D144" s="7"/>
-      <c r="E144" s="9"/>
     </row>
     <row r="145" ht="17" spans="1:5">
       <c r="A145" s="3" t="s">
@@ -27820,7 +27808,6 @@
         <v>1904</v>
       </c>
       <c r="D145" s="7"/>
-      <c r="E145" s="9"/>
     </row>
     <row r="146" ht="17" spans="1:5">
       <c r="A146" s="3" t="s">
@@ -27833,7 +27820,6 @@
         <v>1917</v>
       </c>
       <c r="D146" s="7"/>
-      <c r="E146" s="9"/>
     </row>
     <row r="147" ht="17" spans="1:5">
       <c r="A147" s="3" t="s">
@@ -27846,7 +27832,6 @@
         <v>1923</v>
       </c>
       <c r="D147" s="7"/>
-      <c r="E147" s="9"/>
     </row>
     <row r="148" ht="17" spans="1:5">
       <c r="A148" s="3" t="s">
@@ -27859,7 +27844,6 @@
         <v>1927</v>
       </c>
       <c r="D148" s="7"/>
-      <c r="E148" s="9"/>
     </row>
     <row r="149" ht="17" spans="1:5">
       <c r="A149" s="3" t="s">
@@ -27872,7 +27856,6 @@
         <v>1932</v>
       </c>
       <c r="D149" s="7"/>
-      <c r="E149" s="9"/>
     </row>
     <row r="150" ht="17" spans="1:5">
       <c r="A150" s="3" t="s">
@@ -27885,7 +27868,6 @@
         <v>1936</v>
       </c>
       <c r="D150" s="7"/>
-      <c r="E150" s="9"/>
     </row>
     <row r="151" ht="17" spans="1:5">
       <c r="A151" s="3" t="s">
@@ -27898,7 +27880,6 @@
         <v>1945</v>
       </c>
       <c r="D151" s="7"/>
-      <c r="E151" s="9"/>
     </row>
     <row r="152" ht="17" spans="1:5">
       <c r="A152" s="3" t="s">
@@ -27911,7 +27892,6 @@
         <v>1953</v>
       </c>
       <c r="D152" s="7"/>
-      <c r="E152" s="9"/>
     </row>
     <row r="153" ht="17" spans="1:5">
       <c r="A153" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32000" windowHeight="16220"/>
+    <workbookView windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -2254,7 +2254,7 @@
     <t>4、听书页浏览，上滑5次，下滑5次</t>
   </si>
   <si>
-    <t>5、点击推荐进入首页</t>
+    <t>5、点击推荐进入首页（可能需要左滑）</t>
   </si>
   <si>
     <t>6、点击完本榜，进入完本榜页面</t>
@@ -2263,13 +2263,13 @@
     <t>7、左滑2次，右滑2次，浏览完本榜单</t>
   </si>
   <si>
-    <t>8、点击口碑榜，进入口碑榜页面</t>
+    <t>8、点击巅峰榜，进入巅峰榜页面</t>
   </si>
   <si>
     <t>9、左滑2次，右滑2次，浏览口碑榜单</t>
   </si>
   <si>
-    <t>10、点击高分榜，进入高分榜页面</t>
+    <t>10、点击新书榜，进入新书榜页面</t>
   </si>
   <si>
     <t>11、左滑2次，右滑2次，浏览高分榜单</t>
@@ -2302,7 +2302,7 @@
     <t>5、侧滑返回到首页</t>
   </si>
   <si>
-    <t>6、点击底部短剧，进入短剧推荐页面</t>
+    <t>6、点击短剧，进入短剧推荐页面</t>
   </si>
   <si>
     <t>7、短剧推荐页面滑动，上滑10次</t>
@@ -2314,7 +2314,7 @@
     <t>9、首页上滑3次，下滑3次</t>
   </si>
   <si>
-    <t>10、点击底部音乐</t>
+    <t>10、点击底部音乐（听歌）</t>
   </si>
   <si>
     <t>开心消消乐</t>
@@ -2428,13 +2428,13 @@
     <t>6、侧滑退出评论</t>
   </si>
   <si>
-    <t>7、点击追剧</t>
-  </si>
-  <si>
-    <t>8、点击剧场</t>
-  </si>
-  <si>
-    <t>9、点击右上角搜索</t>
+    <t>7、点击剧场</t>
+  </si>
+  <si>
+    <t>8、再点击剧场</t>
+  </si>
+  <si>
+    <t>9、点击上方搜索</t>
   </si>
   <si>
     <t>10、搜索仙帝</t>
@@ -26763,7 +26763,7 @@
       <c r="C58" s="3" t="s">
         <v>1540</v>
       </c>
-      <c r="D58" s="7"/>
+      <c r="D58" s="5"/>
     </row>
     <row r="59" ht="17" spans="1:4">
       <c r="A59" s="3" t="s">
@@ -26775,7 +26775,7 @@
       <c r="C59" s="3" t="s">
         <v>2114</v>
       </c>
-      <c r="D59" s="7"/>
+      <c r="D59" s="5"/>
     </row>
     <row r="60" ht="17" spans="1:4">
       <c r="A60" s="3" t="s">
@@ -26787,7 +26787,7 @@
       <c r="C60" s="3" t="s">
         <v>458</v>
       </c>
-      <c r="D60" s="7"/>
+      <c r="D60" s="5"/>
     </row>
     <row r="61" ht="17" spans="1:4">
       <c r="A61" s="3" t="s">
@@ -26799,7 +26799,7 @@
       <c r="C61" s="3" t="s">
         <v>481</v>
       </c>
-      <c r="D61" s="7"/>
+      <c r="D61" s="5"/>
     </row>
     <row r="62" ht="17" spans="1:4">
       <c r="A62" s="3" t="s">
@@ -26811,7 +26811,7 @@
       <c r="C62" s="3" t="s">
         <v>491</v>
       </c>
-      <c r="D62" s="7"/>
+      <c r="D62" s="5"/>
     </row>
     <row r="63" ht="17" spans="1:4">
       <c r="A63" s="3" t="s">
@@ -26823,7 +26823,7 @@
       <c r="C63" s="3" t="s">
         <v>516</v>
       </c>
-      <c r="D63" s="7"/>
+      <c r="D63" s="5"/>
     </row>
     <row r="64" ht="17" spans="1:4">
       <c r="A64" s="3" t="s">
@@ -26835,7 +26835,7 @@
       <c r="C64" s="3" t="s">
         <v>535</v>
       </c>
-      <c r="D64" s="7"/>
+      <c r="D64" s="5"/>
     </row>
     <row r="65" ht="17" spans="1:4">
       <c r="A65" s="3" t="s">
@@ -26847,7 +26847,7 @@
       <c r="C65" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="D65" s="7"/>
+      <c r="D65" s="5"/>
     </row>
     <row r="66" ht="17" spans="1:4">
       <c r="A66" s="3" t="s">
@@ -26859,7 +26859,7 @@
       <c r="C66" s="3" t="s">
         <v>555</v>
       </c>
-      <c r="D66" s="7"/>
+      <c r="D66" s="5"/>
     </row>
     <row r="67" ht="17" spans="1:4">
       <c r="A67" s="3" t="s">
@@ -26871,7 +26871,7 @@
       <c r="C67" s="3" t="s">
         <v>566</v>
       </c>
-      <c r="D67" s="7"/>
+      <c r="D67" s="5"/>
     </row>
     <row r="68" ht="17" spans="1:4">
       <c r="A68" s="3" t="s">
@@ -26883,7 +26883,7 @@
       <c r="C68" s="3" t="s">
         <v>575</v>
       </c>
-      <c r="D68" s="7"/>
+      <c r="D68" s="5"/>
     </row>
     <row r="69" ht="17" spans="1:4">
       <c r="A69" s="3" t="s">
@@ -26895,7 +26895,7 @@
       <c r="C69" s="3" t="s">
         <v>598</v>
       </c>
-      <c r="D69" s="7"/>
+      <c r="D69" s="5"/>
     </row>
     <row r="70" ht="17" spans="1:4">
       <c r="A70" s="3" t="s">
@@ -26907,7 +26907,7 @@
       <c r="C70" s="3" t="s">
         <v>617</v>
       </c>
-      <c r="D70" s="7"/>
+      <c r="D70" s="5"/>
     </row>
     <row r="71" ht="17" spans="1:4">
       <c r="A71" s="3" t="s">
@@ -26919,7 +26919,7 @@
       <c r="C71" s="3" t="s">
         <v>651</v>
       </c>
-      <c r="D71" s="7"/>
+      <c r="D71" s="5"/>
     </row>
     <row r="72" ht="17" spans="1:4">
       <c r="A72" s="3" t="s">
@@ -26931,7 +26931,7 @@
       <c r="C72" s="3" t="s">
         <v>663</v>
       </c>
-      <c r="D72" s="7"/>
+      <c r="D72" s="5"/>
     </row>
     <row r="73" ht="17" spans="1:4">
       <c r="A73" s="3" t="s">
@@ -26943,7 +26943,7 @@
       <c r="C73" s="3" t="s">
         <v>677</v>
       </c>
-      <c r="D73" s="7"/>
+      <c r="D73" s="5"/>
     </row>
     <row r="74" ht="17" spans="1:4">
       <c r="A74" s="3" t="s">
@@ -26955,7 +26955,7 @@
       <c r="C74" s="3" t="s">
         <v>688</v>
       </c>
-      <c r="D74" s="7"/>
+      <c r="D74" s="5"/>
     </row>
     <row r="75" ht="17" spans="1:4">
       <c r="A75" s="3" t="s">
@@ -26967,7 +26967,7 @@
       <c r="C75" s="3" t="s">
         <v>710</v>
       </c>
-      <c r="D75" s="7"/>
+      <c r="D75" s="5"/>
     </row>
     <row r="76" ht="17" spans="1:4">
       <c r="A76" s="3" t="s">
@@ -26979,7 +26979,7 @@
       <c r="C76" s="3" t="s">
         <v>718</v>
       </c>
-      <c r="D76" s="7"/>
+      <c r="D76" s="5"/>
     </row>
     <row r="77" ht="17" spans="1:4">
       <c r="A77" s="3" t="s">
@@ -26991,7 +26991,7 @@
       <c r="C77" s="3" t="s">
         <v>732</v>
       </c>
-      <c r="D77" s="7"/>
+      <c r="D77" s="5"/>
     </row>
     <row r="78" ht="17" spans="1:4">
       <c r="A78" s="3" t="s">
@@ -27003,7 +27003,7 @@
       <c r="C78" s="3" t="s">
         <v>743</v>
       </c>
-      <c r="D78" s="7"/>
+      <c r="D78" s="5"/>
     </row>
     <row r="79" ht="17" spans="1:4">
       <c r="A79" s="3" t="s">
@@ -27015,7 +27015,7 @@
       <c r="C79" s="3" t="s">
         <v>746</v>
       </c>
-      <c r="D79" s="7"/>
+      <c r="D79" s="5"/>
     </row>
     <row r="80" ht="17" spans="1:4">
       <c r="A80" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16220"/>
+    <workbookView windowHeight="16220" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -27027,7 +27027,7 @@
       <c r="C80" s="3" t="s">
         <v>751</v>
       </c>
-      <c r="D80" s="7"/>
+      <c r="D80" s="5"/>
     </row>
     <row r="81" ht="17" spans="1:4">
       <c r="A81" s="3" t="s">
@@ -27039,7 +27039,7 @@
       <c r="C81" s="3" t="s">
         <v>774</v>
       </c>
-      <c r="D81" s="7"/>
+      <c r="D81" s="5"/>
     </row>
     <row r="82" ht="17" spans="1:4">
       <c r="A82" s="3" t="s">
@@ -27051,7 +27051,7 @@
       <c r="C82" s="3" t="s">
         <v>792</v>
       </c>
-      <c r="D82" s="7"/>
+      <c r="D82" s="5"/>
     </row>
     <row r="83" ht="17" spans="1:4">
       <c r="A83" s="3" t="s">
@@ -27063,7 +27063,7 @@
       <c r="C83" s="3" t="s">
         <v>801</v>
       </c>
-      <c r="D83" s="7"/>
+      <c r="D83" s="5"/>
     </row>
     <row r="84" ht="17" spans="1:4">
       <c r="A84" s="3" t="s">
@@ -27075,7 +27075,7 @@
       <c r="C84" s="3" t="s">
         <v>882</v>
       </c>
-      <c r="D84" s="7"/>
+      <c r="D84" s="5"/>
     </row>
     <row r="85" ht="17" spans="1:4">
       <c r="A85" s="3" t="s">
@@ -27087,7 +27087,7 @@
       <c r="C85" s="3" t="s">
         <v>897</v>
       </c>
-      <c r="D85" s="7"/>
+      <c r="D85" s="5"/>
     </row>
     <row r="86" ht="17" spans="1:4">
       <c r="A86" s="3" t="s">
@@ -27099,7 +27099,7 @@
       <c r="C86" s="3" t="s">
         <v>912</v>
       </c>
-      <c r="D86" s="7"/>
+      <c r="D86" s="5"/>
     </row>
     <row r="87" ht="17" spans="1:4">
       <c r="A87" s="3" t="s">
@@ -27111,7 +27111,7 @@
       <c r="C87" s="3" t="s">
         <v>924</v>
       </c>
-      <c r="D87" s="7"/>
+      <c r="D87" s="5"/>
     </row>
     <row r="88" ht="17" spans="1:4">
       <c r="A88" s="3" t="s">
@@ -27123,7 +27123,7 @@
       <c r="C88" s="3" t="s">
         <v>946</v>
       </c>
-      <c r="D88" s="7"/>
+      <c r="D88" s="5"/>
     </row>
     <row r="89" ht="17" spans="1:4">
       <c r="A89" s="3" t="s">
@@ -27135,7 +27135,7 @@
       <c r="C89" s="3" t="s">
         <v>977</v>
       </c>
-      <c r="D89" s="7"/>
+      <c r="D89" s="5"/>
     </row>
     <row r="90" ht="17" spans="1:4">
       <c r="A90" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -27147,7 +27147,7 @@
       <c r="C90" s="3" t="s">
         <v>993</v>
       </c>
-      <c r="D90" s="7"/>
+      <c r="D90" s="5"/>
     </row>
     <row r="91" ht="17" spans="1:4">
       <c r="A91" s="3" t="s">
@@ -27159,7 +27159,7 @@
       <c r="C91" s="3" t="s">
         <v>1005</v>
       </c>
-      <c r="D91" s="7"/>
+      <c r="D91" s="5"/>
     </row>
     <row r="92" ht="17" spans="1:4">
       <c r="A92" s="3" t="s">
@@ -27231,7 +27231,7 @@
       <c r="C97" s="3" t="s">
         <v>1168</v>
       </c>
-      <c r="D97" s="7"/>
+      <c r="D97" s="5"/>
     </row>
     <row r="98" ht="17" spans="1:4">
       <c r="A98" s="3" t="s">
@@ -27243,7 +27243,7 @@
       <c r="C98" s="3" t="s">
         <v>1202</v>
       </c>
-      <c r="D98" s="8"/>
+      <c r="D98" s="5"/>
     </row>
     <row r="99" ht="17" spans="1:4">
       <c r="A99" s="3" t="s">
@@ -27279,7 +27279,7 @@
       <c r="C101" s="3" t="s">
         <v>1279</v>
       </c>
-      <c r="D101" s="8"/>
+      <c r="D101" s="5"/>
     </row>
     <row r="102" ht="17" spans="1:4">
       <c r="A102" s="3" t="s">
@@ -27291,7 +27291,7 @@
       <c r="C102" s="3" t="s">
         <v>1292</v>
       </c>
-      <c r="D102" s="8"/>
+      <c r="D102" s="5"/>
     </row>
     <row r="103" ht="17" spans="1:4">
       <c r="A103" s="3" t="s">
@@ -27303,7 +27303,7 @@
       <c r="C103" s="3" t="s">
         <v>1297</v>
       </c>
-      <c r="D103" s="8"/>
+      <c r="D103" s="5"/>
     </row>
     <row r="104" ht="17" spans="1:4">
       <c r="A104" s="3" t="s">
@@ -27315,7 +27315,7 @@
       <c r="C104" s="3" t="s">
         <v>1304</v>
       </c>
-      <c r="D104" s="8"/>
+      <c r="D104" s="5"/>
     </row>
     <row r="105" ht="17" spans="1:4">
       <c r="A105" s="3" t="s">
@@ -27327,7 +27327,7 @@
       <c r="C105" s="3" t="s">
         <v>1320</v>
       </c>
-      <c r="D105" s="8"/>
+      <c r="D105" s="5"/>
     </row>
     <row r="106" ht="17" spans="1:4">
       <c r="A106" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16220" activeTab="1"/>
+    <workbookView windowHeight="16220"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -4408,7 +4408,28 @@
     <t>10、侧滑返回去哪儿旅行主页</t>
   </si>
   <si>
-    <t>11、点击火车高铁，进入搜索页面</t>
+    <r>
+      <t>11、点击火车高铁，</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>有弹窗（点击放弃权益）</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，进入搜索页面</t>
+    </r>
   </si>
   <si>
     <t>12、点击搜索，进入车次选择页面</t>
@@ -4549,7 +4570,7 @@
     <t>4、上滑2次，下滑2次浏览国歌</t>
   </si>
   <si>
-    <t>6、点击下方播放按钮，播放15S后暂停</t>
+    <t>6、点击下方播放按钮（如果播放中15s后直接暂停），播放15S后暂停</t>
   </si>
   <si>
     <t>7、点击右下角我的</t>
@@ -4561,7 +4582,7 @@
     <t>9、返回首页</t>
   </si>
   <si>
-    <t>10、点击右下角⋮打开播放列表</t>
+    <t>10、点击右上角三横线</t>
   </si>
   <si>
     <t>11、返回汽水音乐主界面</t>
@@ -5092,13 +5113,13 @@
     <t>2、主页浏览，上下各滑动5次</t>
   </si>
   <si>
-    <t>3、点击天气主页面右下方三点三线</t>
+    <t>3、点击天气主页面左下方三点三线</t>
   </si>
   <si>
     <t>4、点击左上按钮，再返回（单击空白）</t>
   </si>
   <si>
-    <t>5、点击城市管理界面的第一个城市</t>
+    <t>5、主页浏览</t>
   </si>
   <si>
     <t>6、滑动切换不同城市，左滑5次，右滑5次，重复操作5次</t>
@@ -5326,10 +5347,10 @@
     <t>4、向上抛滑3次，浏览运动页面</t>
   </si>
   <si>
-    <t>5、点击底部天天低价，进入天天低价页面</t>
-  </si>
-  <si>
-    <t>6、上滑2次，下滑2次，浏览天天低价页面</t>
+    <t>5、点击底部分类，进入分类页面</t>
+  </si>
+  <si>
+    <t>6、上滑2次，下滑2次，浏览分类页面</t>
   </si>
   <si>
     <t>7、返回唯品会主界面</t>
@@ -19242,7 +19263,7 @@
       <c r="A1344" s="9"/>
       <c r="B1344" s="9"/>
       <c r="C1344" s="9"/>
-      <c r="D1344" s="9" t="s">
+      <c r="D1344" s="11" t="s">
         <v>1440</v>
       </c>
     </row>
@@ -21032,7 +21053,7 @@
       <c r="A1555" s="9"/>
       <c r="B1555" s="9"/>
       <c r="C1555" s="9"/>
-      <c r="D1555" s="9" t="s">
+      <c r="D1555" s="10" t="s">
         <v>1671</v>
       </c>
     </row>

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -27639,7 +27639,7 @@
       <c r="C126" s="3" t="s">
         <v>1660</v>
       </c>
-      <c r="D126" s="7"/>
+      <c r="D126" s="5"/>
     </row>
     <row r="127" ht="17" spans="1:4">
       <c r="A127" s="3" t="s">
@@ -27651,7 +27651,7 @@
       <c r="C127" s="3" t="s">
         <v>1665</v>
       </c>
-      <c r="D127" s="7"/>
+      <c r="D127" s="5"/>
     </row>
     <row r="128" ht="17" spans="1:4">
       <c r="A128" s="3" t="s">

--- a/动态性能模型测试用例7.xlsx
+++ b/动态性能模型测试用例7.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16220"/>
+    <workbookView windowHeight="16660"/>
   </bookViews>
   <sheets>
     <sheet name="新-7.0.2模型测试步骤" sheetId="7" r:id="rId1"/>
@@ -7333,7 +7333,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -7386,6 +7386,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -21415,7 +21418,7 @@
       <c r="A1598" s="9"/>
       <c r="B1598" s="9"/>
       <c r="C1598" s="9"/>
-      <c r="D1598" s="9" t="s">
+      <c r="D1598" s="18" t="s">
         <v>1715</v>
       </c>
     </row>
